--- a/artfynd/A 27924-2025 artfynd.xlsx
+++ b/artfynd/A 27924-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>126739863</v>
       </c>
       <c r="B3" t="n">
-        <v>97445</v>
+        <v>97520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>126739877</v>
       </c>
       <c r="B4" t="n">
-        <v>97231</v>
+        <v>97306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>126739678</v>
       </c>
       <c r="B5" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27924-2025 artfynd.xlsx
+++ b/artfynd/A 27924-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>126739863</v>
       </c>
       <c r="B3" t="n">
-        <v>97520</v>
+        <v>97526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>126739877</v>
       </c>
       <c r="B4" t="n">
-        <v>97306</v>
+        <v>97312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>126739678</v>
       </c>
       <c r="B5" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27924-2025 artfynd.xlsx
+++ b/artfynd/A 27924-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>126739863</v>
       </c>
       <c r="B3" t="n">
-        <v>97526</v>
+        <v>97527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>126739877</v>
       </c>
       <c r="B4" t="n">
-        <v>97312</v>
+        <v>97313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>126739678</v>
       </c>
       <c r="B5" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27924-2025 artfynd.xlsx
+++ b/artfynd/A 27924-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126739811</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>126739863</v>
       </c>
       <c r="B3" t="n">
-        <v>97527</v>
+        <v>97531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>126739877</v>
       </c>
       <c r="B4" t="n">
-        <v>97313</v>
+        <v>97317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>126739678</v>
       </c>
       <c r="B5" t="n">
-        <v>96046</v>
+        <v>96050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27924-2025 artfynd.xlsx
+++ b/artfynd/A 27924-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126739811</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>126739863</v>
       </c>
       <c r="B3" t="n">
-        <v>97531</v>
+        <v>97520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>126739877</v>
       </c>
       <c r="B4" t="n">
-        <v>97317</v>
+        <v>97306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>126739678</v>
       </c>
       <c r="B5" t="n">
-        <v>96050</v>
+        <v>96039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
